--- a/dcf/TEM.xlsx
+++ b/dcf/TEM.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1126,25 +1126,25 @@
         <v>1.5</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>9.984955901272258</v>
+        <v>7.833832587225376</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>9.589043993291563</v>
+        <v>7.518273662308887</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>9.209540810422425</v>
+        <v>7.215708434724749</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>8.845685077822678</v>
+        <v>6.925536426610432</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>8.496754281533763</v>
+        <v>6.647187661079171</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>8.162062530266248</v>
+        <v>6.380120982201481</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>7.84095854385291</v>
+        <v>6.123822474410968</v>
       </c>
     </row>
     <row r="6">
@@ -1152,25 +1152,25 @@
         <v>2.5</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>14.39556433548544</v>
+        <v>11.2849262835458</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>13.81876144563992</v>
+        <v>10.82782867149662</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>13.26649455795795</v>
+        <v>10.39008396889774</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>12.73760567573199</v>
+        <v>9.970781281682346</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>12.23099645710641</v>
+        <v>9.569056565307037</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>11.74562489659883</v>
+        <v>9.184090021232194</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>11.28050220443448</v>
+        <v>8.815103648494491</v>
       </c>
     </row>
     <row r="7">
@@ -1178,25 +1178,25 @@
         <v>3.5</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>18.80617276969862</v>
+        <v>14.73601997986623</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>18.04847889798828</v>
+        <v>14.13738368068436</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>17.32344830549348</v>
+        <v>13.56445950307074</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>16.62952627364131</v>
+        <v>13.01602613675426</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>15.96523863267906</v>
+        <v>12.4909254695349</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>15.32918726293142</v>
+        <v>11.98805906026291</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>14.72004586501605</v>
+        <v>11.50638482257801</v>
       </c>
     </row>
     <row r="8">
@@ -1204,25 +1204,25 @@
         <v>4.5</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>23.21678120391179</v>
+        <v>18.18711367618665</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>22.27819635033663</v>
+        <v>17.44693868987209</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>21.380402053029</v>
+        <v>16.73883503724374</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>20.52144687155063</v>
+        <v>16.06127099182617</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>19.6994808082517</v>
+        <v>15.41279437376276</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>18.912749629264</v>
+        <v>14.79202809929362</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>18.15958952559761</v>
+        <v>14.19766599666154</v>
       </c>
     </row>
     <row r="9">
@@ -1230,25 +1230,25 @@
         <v>5.5</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>27.62738963812497</v>
+        <v>21.63820737250708</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>26.50791380268499</v>
+        <v>20.75649369905983</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>25.43735580056453</v>
+        <v>19.91321057141673</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>24.41336746945995</v>
+        <v>19.10651584689808</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>23.43372298382435</v>
+        <v>18.33466327799063</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>22.49631199559658</v>
+        <v>17.59599713832434</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>21.59913318617918</v>
+        <v>16.88894717074506</v>
       </c>
     </row>
     <row r="10">
@@ -1256,25 +1256,25 @@
         <v>6.5</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>32.03799807233814</v>
+        <v>25.0893010688275</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>30.73763125503334</v>
+        <v>24.06604870824757</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>29.49430954810005</v>
+        <v>23.08758610558973</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>28.30528806736926</v>
+        <v>22.15176070196999</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>27.167965159397</v>
+        <v>21.2565321822185</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>26.07987436192916</v>
+        <v>20.39996617735505</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>25.03867684676075</v>
+        <v>19.58022834482858</v>
       </c>
     </row>
     <row r="11">
@@ -1282,25 +1282,25 @@
         <v>7.5</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>36.44860650655133</v>
+        <v>28.54039476514793</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>34.9673487073817</v>
+        <v>27.3756037174353</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>33.55126329563558</v>
+        <v>26.26196163976272</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>32.19720866527858</v>
+        <v>25.1970055570419</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>30.90220733496965</v>
+        <v>24.17840108644636</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>29.66343672826175</v>
+        <v>23.20393521638576</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>28.47822050734232</v>
+        <v>22.2715095189121</v>
       </c>
     </row>
     <row r="13">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>3.667461193130503</v>
+        <v>3.878744630073444</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24415,7 +24415,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24567,13 +24567,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>20.52144687155063</v>
+        <v>16.06127099182617</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>34.50002360413652</v>
+        <v>26.52268100460786</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>9.956665047416736</v>
+        <v>7.887404207090819</v>
       </c>
     </row>
     <row r="59">
